--- a/Result/profitability/4927.xlsx
+++ b/Result/profitability/4927.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.04</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.12125</v>
+        <v>-2.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2050000000000001</v>
+        <v>-0.5812499999999998</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.71875</v>
+        <v>-1.5925</v>
       </c>
       <c r="N3" t="n">
-        <v>1.9575</v>
+        <v>1.275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1075</v>
+        <v>-1.235</v>
       </c>
       <c r="N4" t="n">
-        <v>4.16625</v>
+        <v>2.82625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.82375</v>
+        <v>-0.9562500000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>5.71125</v>
+        <v>4.44</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -8812,6 +8812,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4927</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2941</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3115</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-174</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-565</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-19.23%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>-61</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-626</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-624</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-2.54625</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-3.1275</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.7400000000000002</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-0.2387096774193549</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>-0.5268214571657326</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.8153846153846152</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>-10.17</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>-2.387323943661972</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
